--- a/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
+++ b/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
@@ -30,7 +30,7 @@
     <sheet name="INSTRUCCIONES" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 

--- a/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
+++ b/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>SUMIF(CxP!D:D,"USD",CxP!H:H)</f>
+        <f>SUMIF(CxP!D3:D1000,"USD",CxP!H3:H1000)</f>
         <v/>
       </c>
     </row>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>SUMIF(CxP!D:D,"CRC",CxP!C:C)</f>
+        <f>SUMIF(CxP!D3:D1000,"CRC",CxP!C3:C1000)</f>
         <v/>
       </c>
     </row>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>COUNTIF(CxP!G:G,"&gt;0")</f>
+        <f>COUNTIF(CxP!G3:G1000,"&gt;0")</f>
         <v/>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B8" s="6">
-        <f>AVERAGE(CxP!G:G)</f>
+        <f>AVERAGE(CxP!G3:G1000)</f>
         <v/>
       </c>
     </row>
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>SUMIF(CxC!D:D,"USD",CxC!H:H)</f>
+        <f>SUMIF(CxC!D3:D1000,"USD",CxC!H3:H1000)</f>
         <v/>
       </c>
     </row>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>SUMIF(CxC!D:D,"CRC",CxC!C:C)</f>
+        <f>SUMIF(CxC!D3:D1000,"CRC",CxC!C3:C1000)</f>
         <v/>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B13" s="6">
-        <f>COUNTIF(CxC!G:G,"&gt;60")</f>
+        <f>COUNTIF(CxC!G3:G1000,"&gt;60")</f>
         <v/>
       </c>
     </row>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B14" s="6">
-        <f>AVERAGE(CxC!G:G)</f>
+        <f>AVERAGE(CxC!G3:G1000)</f>
         <v/>
       </c>
     </row>
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>IFERROR(SUMIF(CxC!G:G,"&gt;90",CxC!H:H)/SUM(CxC!H:H)*100,0)</f>
+        <f>IFERROR(SUMIF(CxC!G3:G1000,"&gt;90",CxC!H3:H1000)/SUM(CxC!H3:H1000)*100,0)</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="B31" s="6">
-        <f>IFERROR(AVERAGE(CxC!G:G),0)</f>
+        <f>IFERROR(AVERAGE(CxC!G3:G1000),0)</f>
         <v/>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="B32" s="6">
-        <f>IFERROR(AVERAGE(CxP!G:G),0)</f>
+        <f>IFERROR(AVERAGE(CxP!G3:G1000),0)</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="B53" s="6">
-        <f>COUNTIF(CxC!G:G,"&gt;90")</f>
+        <f>COUNTIF(CxC!G3:G1000,"&gt;90")</f>
         <v/>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>SUM(CxP!H:H)</f>
+        <f>SUM(CxP!H3:H1000)</f>
         <v/>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>SUM(CxC!H:H)</f>
+        <f>SUM(CxC!H3:H1000)</f>
         <v/>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>SUM(CxC!H:H)</f>
+        <f>SUM(CxC!H3:H1000)</f>
         <v/>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>SUM(CxP!H:H)</f>
+        <f>SUM(CxP!H3:H1000)</f>
         <v/>
       </c>
     </row>
@@ -37269,47 +37269,47 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>FILTER(TRANSACCIONES!B:B,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"Sin CxP pendientes")</f>
+        <f>FILTER(TRANSACCIONES!B3:B1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"Sin CxP pendientes")</f>
         <v/>
       </c>
       <c r="B3" s="19">
-        <f>FILTER(TRANSACCIONES!A:A,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!A3:A1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="C3" s="20">
-        <f>FILTER(TRANSACCIONES!F:F,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!F3:F1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>FILTER(TRANSACCIONES!E:E,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!E3:E1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>FILTER(TRANSACCIONES!G:G,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!G3:G1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>FILTER(TRANSACCIONES!M:M,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!M3:M1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>FILTER(TRANSACCIONES!S:S,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!S3:S1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>FILTER(TRANSACCIONES!T:T,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!T3:T1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>FILTER(TRANSACCIONES!N:N,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!N3:N1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>FILTER(TRANSACCIONES!U:U,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!U3:U1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="K3">
-        <f>FILTER(TRANSACCIONES!V:V,(TRANSACCIONES!C:C="CxP")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!V3:V1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -37417,47 +37417,47 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>FILTER(TRANSACCIONES!B:B,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"Sin CxC pendientes")</f>
+        <f>FILTER(TRANSACCIONES!B3:B1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"Sin CxC pendientes")</f>
         <v/>
       </c>
       <c r="B3" s="19">
-        <f>FILTER(TRANSACCIONES!A:A,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!A3:A1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="C3" s="20">
-        <f>FILTER(TRANSACCIONES!F:F,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!F3:F1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>FILTER(TRANSACCIONES!E:E,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!E3:E1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>FILTER(TRANSACCIONES!G:G,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!G3:G1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>FILTER(TRANSACCIONES!M:M,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!M3:M1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>FILTER(TRANSACCIONES!S:S,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!S3:S1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>FILTER(TRANSACCIONES!T:T,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!T3:T1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>FILTER(TRANSACCIONES!N:N,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!N3:N1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>FILTER(TRANSACCIONES!U:U,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!U3:U1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="K3">
-        <f>FILTER(TRANSACCIONES!W:W,(TRANSACCIONES!C:C="CxC")*(TRANSACCIONES!M:M="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!W3:W1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
         <v/>
       </c>
       <c r="L3" t="inlineStr"/>

--- a/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
+++ b/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>IFERROR(B19/B20,0)</f>
+        <f>IFERROR(B18/B19,0)</f>
         <v/>
       </c>
     </row>

--- a/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
+++ b/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
@@ -4101,26 +4101,21 @@
         <f>IF(AND(A3&lt;&gt;"",ISNUMBER(A3),B3&lt;&gt;"",C3&lt;&gt;"",OR(E3="USD",E3="CRC"),F3&gt;0,ISNUMBER(Q3),Q3&gt;0),"✓ OK","✗ ERROR: Revisa datos")</f>
         <v/>
       </c>
-      <c r="S3" s="6">
-        <f>IF(A3&lt;&gt;"",TODAY()-A3,"")</f>
-        <v/>
-      </c>
-      <c r="T3" s="4">
-        <f>IF(E3="USD",F3,IF(E3="CRC",F3/CONFIG!$B$5,""))</f>
-        <v/>
-      </c>
-      <c r="U3" s="19">
-        <f>IF(A3&lt;&gt;"",A3+30,"")</f>
-        <v/>
-      </c>
-      <c r="V3">
-        <f>IF(AND(C3="CxP",S3&gt;60),"Alta",IF(AND(C3="CxP",S3&gt;30),"Media",IF(C3="CxP","Baja","")))</f>
-        <v/>
-      </c>
-      <c r="W3">
-        <f>IF(AND(C3="CxC",S3&gt;90),"Alta",IF(AND(C3="CxC",S3&gt;60),"Media",IF(C3="CxC","Baja","")))</f>
-        <v/>
-      </c>
+      <c r="S3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>3390.740740740741</v>
+      </c>
+      <c r="U3" s="19" t="n">
+        <v>46008</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="n">
@@ -4198,26 +4193,21 @@
         <f>IF(AND(A4&lt;&gt;"",ISNUMBER(A4),B4&lt;&gt;"",C4&lt;&gt;"",OR(E4="USD",E4="CRC"),F4&gt;0,ISNUMBER(Q4),Q4&gt;0),"✓ OK","✗ ERROR: Revisa datos")</f>
         <v/>
       </c>
-      <c r="S4" s="6">
-        <f>IF(A4&lt;&gt;"",TODAY()-A4,"")</f>
-        <v/>
-      </c>
-      <c r="T4" s="4">
-        <f>IF(E4="USD",F4,IF(E4="CRC",F4/CONFIG!$B$5,""))</f>
-        <v/>
-      </c>
-      <c r="U4" s="19">
-        <f>IF(A4&lt;&gt;"",A4+30,"")</f>
-        <v/>
-      </c>
-      <c r="V4">
-        <f>IF(AND(C4="CxP",S4&gt;60),"Alta",IF(AND(C4="CxP",S4&gt;30),"Media",IF(C4="CxP","Baja","")))</f>
-        <v/>
-      </c>
-      <c r="W4">
-        <f>IF(AND(C4="CxC",S4&gt;90),"Alta",IF(AND(C4="CxC",S4&gt;60),"Media",IF(C4="CxC","Baja","")))</f>
-        <v/>
-      </c>
+      <c r="S4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>3240.740740740741</v>
+      </c>
+      <c r="U4" s="19" t="n">
+        <v>46008</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="19" t="n">
@@ -4295,26 +4285,21 @@
         <f>IF(AND(A5&lt;&gt;"",ISNUMBER(A5),B5&lt;&gt;"",C5&lt;&gt;"",OR(E5="USD",E5="CRC"),F5&gt;0,ISNUMBER(Q5),Q5&gt;0),"✓ OK","✗ ERROR: Revisa datos")</f>
         <v/>
       </c>
-      <c r="S5" s="6">
-        <f>IF(A5&lt;&gt;"",TODAY()-A5,"")</f>
-        <v/>
-      </c>
-      <c r="T5" s="4">
-        <f>IF(E5="USD",F5,IF(E5="CRC",F5/CONFIG!$B$5,""))</f>
-        <v/>
-      </c>
-      <c r="U5" s="19">
-        <f>IF(A5&lt;&gt;"",A5+30,"")</f>
-        <v/>
-      </c>
-      <c r="V5">
-        <f>IF(AND(C5="CxP",S5&gt;60),"Alta",IF(AND(C5="CxP",S5&gt;30),"Media",IF(C5="CxP","Baja","")))</f>
-        <v/>
-      </c>
-      <c r="W5">
-        <f>IF(AND(C5="CxC",S5&gt;90),"Alta",IF(AND(C5="CxC",S5&gt;60),"Media",IF(C5="CxC","Baja","")))</f>
-        <v/>
-      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>2500</v>
+      </c>
+      <c r="U5" s="19" t="n">
+        <v>46008</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="19" t="n">
@@ -4392,26 +4377,21 @@
         <f>IF(AND(A6&lt;&gt;"",ISNUMBER(A6),B6&lt;&gt;"",C6&lt;&gt;"",OR(E6="USD",E6="CRC"),F6&gt;0,ISNUMBER(Q6),Q6&gt;0),"✓ OK","✗ ERROR: Revisa datos")</f>
         <v/>
       </c>
-      <c r="S6" s="6">
-        <f>IF(A6&lt;&gt;"",TODAY()-A6,"")</f>
-        <v/>
-      </c>
-      <c r="T6" s="4">
-        <f>IF(E6="USD",F6,IF(E6="CRC",F6/CONFIG!$B$5,""))</f>
-        <v/>
-      </c>
-      <c r="U6" s="19">
-        <f>IF(A6&lt;&gt;"",A6+30,"")</f>
-        <v/>
-      </c>
-      <c r="V6">
-        <f>IF(AND(C6="CxP",S6&gt;60),"Alta",IF(AND(C6="CxP",S6&gt;30),"Media",IF(C6="CxP","Baja","")))</f>
-        <v/>
-      </c>
-      <c r="W6">
-        <f>IF(AND(C6="CxC",S6&gt;90),"Alta",IF(AND(C6="CxC",S6&gt;60),"Media",IF(C6="CxC","Baja","")))</f>
-        <v/>
-      </c>
+      <c r="S6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>5185.185185185185</v>
+      </c>
+      <c r="U6" s="19" t="n">
+        <v>46008</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="19" t="n"/>

--- a/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
+++ b/scripts/python/AlvaroVelasco_Finanzas_v5.0_COMPLETO.xlsx
@@ -37249,47 +37249,47 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>FILTER(TRANSACCIONES!B3:B1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"Sin CxP pendientes")</f>
+        <f>FILTER(TRANSACCIONES!B3:B1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"Sin CxP pendientes")</f>
         <v/>
       </c>
       <c r="B3" s="19">
-        <f>FILTER(TRANSACCIONES!A3:A1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!A3:A1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="C3" s="20">
-        <f>FILTER(TRANSACCIONES!F3:F1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!F3:F1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>FILTER(TRANSACCIONES!E3:E1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!E3:E1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>FILTER(TRANSACCIONES!G3:G1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!G3:G1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>FILTER(TRANSACCIONES!M3:M1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!M3:M1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>FILTER(TRANSACCIONES!S3:S1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!S3:S1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>FILTER(TRANSACCIONES!T3:T1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!T3:T1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>FILTER(TRANSACCIONES!N3:N1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!N3:N1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>FILTER(TRANSACCIONES!U3:U1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!U3:U1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="K3">
-        <f>FILTER(TRANSACCIONES!V3:V1000,(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!V3:V1000;(TRANSACCIONES!C3:C1000="CxP")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -37397,47 +37397,47 @@
     </row>
     <row r="3">
       <c r="A3">
-        <f>FILTER(TRANSACCIONES!B3:B1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"Sin CxC pendientes")</f>
+        <f>FILTER(TRANSACCIONES!B3:B1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"Sin CxC pendientes")</f>
         <v/>
       </c>
       <c r="B3" s="19">
-        <f>FILTER(TRANSACCIONES!A3:A1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!A3:A1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="C3" s="20">
-        <f>FILTER(TRANSACCIONES!F3:F1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!F3:F1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>FILTER(TRANSACCIONES!E3:E1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!E3:E1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>FILTER(TRANSACCIONES!G3:G1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!G3:G1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>FILTER(TRANSACCIONES!M3:M1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!M3:M1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>FILTER(TRANSACCIONES!S3:S1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!S3:S1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>FILTER(TRANSACCIONES!T3:T1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!T3:T1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="I3">
-        <f>FILTER(TRANSACCIONES!N3:N1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!N3:N1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="J3" s="19">
-        <f>FILTER(TRANSACCIONES!U3:U1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!U3:U1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="K3">
-        <f>FILTER(TRANSACCIONES!W3:W1000,(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente"),"")</f>
+        <f>FILTER(TRANSACCIONES!W3:W1000;(TRANSACCIONES!C3:C1000="CxC")*(TRANSACCIONES!M3:M1000="Pendiente");"")</f>
         <v/>
       </c>
       <c r="L3" t="inlineStr"/>
